--- a/artfynd/A 46918-2024 artfynd.xlsx
+++ b/artfynd/A 46918-2024 artfynd.xlsx
@@ -675,49 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68503535</v>
+        <v>68503964</v>
       </c>
       <c r="B2" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -725,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475963.2624957698</v>
+        <v>475963</v>
       </c>
       <c r="R2" t="n">
-        <v>6245818.652996309</v>
+        <v>6245819</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +749,9 @@
           <t>2017-11-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-11-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,16 +764,17 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>Jonny Svensson</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Ivar Björegren</t>
@@ -807,45 +789,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68503964</v>
+        <v>68503535</v>
       </c>
       <c r="B3" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>4189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475963.2624957698</v>
+        <v>475963</v>
       </c>
       <c r="R3" t="n">
-        <v>6245818.652996309</v>
+        <v>6245819</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,19 +867,9 @@
           <t>2017-11-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-11-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +882,16 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>Jonny Svensson</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Ivar Björegren</t>

--- a/artfynd/A 46918-2024 artfynd.xlsx
+++ b/artfynd/A 46918-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68503964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68503535</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>